--- a/output/yearly_total_coral_cover_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_47_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252863650532691</v>
+        <v>1.274746806860352</v>
       </c>
       <c r="C3" t="n">
-        <v>4.636388836415994</v>
+        <v>4.699475943890894</v>
       </c>
       <c r="D3" t="n">
-        <v>6.025815331707403</v>
+        <v>6.042406867909174</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91506781865609</v>
+        <v>12.01662961866042</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.368980907045577</v>
+        <v>1.439335137044639</v>
       </c>
       <c r="C4" t="n">
-        <v>5.128410496977251</v>
+        <v>5.3248454203969</v>
       </c>
       <c r="D4" t="n">
-        <v>6.299263158502392</v>
+        <v>6.216941561096433</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79665456252522</v>
+        <v>12.98112211853797</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.52988364580132</v>
+        <v>1.655129038822676</v>
       </c>
       <c r="C5" t="n">
-        <v>5.729671747902778</v>
+        <v>6.143622796239575</v>
       </c>
       <c r="D5" t="n">
-        <v>6.567054903939467</v>
+        <v>6.519988143533514</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82661029764357</v>
+        <v>14.31873997859577</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.716554126208553</v>
+        <v>1.907789827755672</v>
       </c>
       <c r="C6" t="n">
-        <v>6.428256024769797</v>
+        <v>7.142301378581348</v>
       </c>
       <c r="D6" t="n">
-        <v>6.94623346001222</v>
+        <v>6.859559262866099</v>
       </c>
       <c r="E6" t="n">
-        <v>15.09104361099057</v>
+        <v>15.90965046920312</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.93869926192852</v>
+        <v>2.178060941031432</v>
       </c>
       <c r="C7" t="n">
-        <v>7.236605887274631</v>
+        <v>8.255693065055299</v>
       </c>
       <c r="D7" t="n">
-        <v>7.339421146579104</v>
+        <v>7.185740220542044</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51472629578225</v>
+        <v>17.61949422662877</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.187793770987019</v>
+        <v>1.365180563960658</v>
       </c>
       <c r="C8" t="n">
-        <v>4.794864379385788</v>
+        <v>5.800195230807971</v>
       </c>
       <c r="D8" t="n">
-        <v>5.5716784830412</v>
+        <v>5.368593750171657</v>
       </c>
       <c r="E8" t="n">
-        <v>11.55433663341401</v>
+        <v>12.53396954494029</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.512386507931219</v>
+        <v>1.71700107983124</v>
       </c>
       <c r="C9" t="n">
-        <v>5.818268465869355</v>
+        <v>7.172654114578638</v>
       </c>
       <c r="D9" t="n">
-        <v>6.058394502130934</v>
+        <v>5.839663310521936</v>
       </c>
       <c r="E9" t="n">
-        <v>13.38904947593151</v>
+        <v>14.72931850493181</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.864539099342582</v>
+        <v>2.079389047226349</v>
       </c>
       <c r="C10" t="n">
-        <v>7.021111265217449</v>
+        <v>8.720715900525519</v>
       </c>
       <c r="D10" t="n">
-        <v>6.51991799054166</v>
+        <v>6.322705320164265</v>
       </c>
       <c r="E10" t="n">
-        <v>15.40556835510169</v>
+        <v>17.12281026791613</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.231590946958301</v>
+        <v>2.439439801327667</v>
       </c>
       <c r="C11" t="n">
-        <v>8.41402297853899</v>
+        <v>10.36854906601073</v>
       </c>
       <c r="D11" t="n">
-        <v>7.041423280151628</v>
+        <v>6.746327709950255</v>
       </c>
       <c r="E11" t="n">
-        <v>17.68703720564892</v>
+        <v>19.55431657728866</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.595476640335377</v>
+        <v>2.804005271802452</v>
       </c>
       <c r="C12" t="n">
-        <v>9.925671094714763</v>
+        <v>12.15552154635434</v>
       </c>
       <c r="D12" t="n">
-        <v>7.499851488570791</v>
+        <v>7.134385950962036</v>
       </c>
       <c r="E12" t="n">
-        <v>20.02099922362093</v>
+        <v>22.09391276911882</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.953405682738531</v>
+        <v>3.135743805800269</v>
       </c>
       <c r="C13" t="n">
-        <v>11.50947067055134</v>
+        <v>13.96130408884781</v>
       </c>
       <c r="D13" t="n">
-        <v>7.976283784534247</v>
+        <v>7.574699462099344</v>
       </c>
       <c r="E13" t="n">
-        <v>22.43916013782412</v>
+        <v>24.67174735674742</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.697029446606951</v>
+        <v>1.803254548206456</v>
       </c>
       <c r="C14" t="n">
-        <v>8.15946224962792</v>
+        <v>9.812823558349974</v>
       </c>
       <c r="D14" t="n">
-        <v>6.075467127915047</v>
+        <v>5.782788502324987</v>
       </c>
       <c r="E14" t="n">
-        <v>15.93195882414992</v>
+        <v>17.39886660888142</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.755561244734146</v>
+        <v>1.839235601567102</v>
       </c>
       <c r="C15" t="n">
-        <v>8.883049577565989</v>
+        <v>10.67578960785996</v>
       </c>
       <c r="D15" t="n">
-        <v>6.071677581776654</v>
+        <v>5.745707891535585</v>
       </c>
       <c r="E15" t="n">
-        <v>16.71028840407679</v>
+        <v>18.26073310096265</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.056751622920025</v>
+        <v>2.11536196086356</v>
       </c>
       <c r="C16" t="n">
-        <v>10.6484282993426</v>
+        <v>12.6986316650753</v>
       </c>
       <c r="D16" t="n">
-        <v>6.56255143390006</v>
+        <v>6.21207732096099</v>
       </c>
       <c r="E16" t="n">
-        <v>19.26773135616269</v>
+        <v>21.02607094689985</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.659408874580214</v>
+        <v>1.682558485446354</v>
       </c>
       <c r="C17" t="n">
-        <v>9.99021555103033</v>
+        <v>11.73076587336654</v>
       </c>
       <c r="D17" t="n">
-        <v>6.095779487915913</v>
+        <v>5.749301088133128</v>
       </c>
       <c r="E17" t="n">
-        <v>17.74540391352646</v>
+        <v>19.16262544694602</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.905405396833337</v>
+        <v>1.906662033894773</v>
       </c>
       <c r="C18" t="n">
-        <v>11.79874208440859</v>
+        <v>13.73794905469915</v>
       </c>
       <c r="D18" t="n">
-        <v>6.528563328379034</v>
+        <v>6.159701080939422</v>
       </c>
       <c r="E18" t="n">
-        <v>20.23271080962096</v>
+        <v>21.80431216953334</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.918511728685032</v>
+        <v>1.89921056881954</v>
       </c>
       <c r="C19" t="n">
-        <v>12.7664802489158</v>
+        <v>14.70185840315979</v>
       </c>
       <c r="D19" t="n">
-        <v>6.628357982515722</v>
+        <v>6.234029199627948</v>
       </c>
       <c r="E19" t="n">
-        <v>21.31334996011655</v>
+        <v>22.83509817160728</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.135507423754705</v>
+        <v>2.094058035681404</v>
       </c>
       <c r="C20" t="n">
-        <v>14.75169191662736</v>
+        <v>16.78496013446181</v>
       </c>
       <c r="D20" t="n">
-        <v>7.070360433921722</v>
+        <v>6.608909560494594</v>
       </c>
       <c r="E20" t="n">
-        <v>23.95755977430379</v>
+        <v>25.4879277306378</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.267740627970949</v>
+        <v>1.234812809970511</v>
       </c>
       <c r="C21" t="n">
-        <v>10.89750750938706</v>
+        <v>12.25786621577666</v>
       </c>
       <c r="D21" t="n">
-        <v>5.889327763189852</v>
+        <v>5.5110014678813</v>
       </c>
       <c r="E21" t="n">
-        <v>18.05457590054786</v>
+        <v>19.00368049362847</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_47_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.274746806860352</v>
+        <v>1.302068845469541</v>
       </c>
       <c r="C3" t="n">
-        <v>4.699475943890894</v>
+        <v>4.650594725696445</v>
       </c>
       <c r="D3" t="n">
-        <v>6.042406867909174</v>
+        <v>6.117706916824906</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01662961866042</v>
+        <v>12.07037048799089</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.439335137044639</v>
+        <v>1.498152258977249</v>
       </c>
       <c r="C4" t="n">
-        <v>5.3248454203969</v>
+        <v>5.221625386803398</v>
       </c>
       <c r="D4" t="n">
-        <v>6.216941561096433</v>
+        <v>6.31416295383554</v>
       </c>
       <c r="E4" t="n">
-        <v>12.98112211853797</v>
+        <v>13.03394059961619</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.655129038822676</v>
+        <v>1.747805120190746</v>
       </c>
       <c r="C5" t="n">
-        <v>6.143622796239575</v>
+        <v>5.974510172330911</v>
       </c>
       <c r="D5" t="n">
-        <v>6.519988143533514</v>
+        <v>6.617265199996401</v>
       </c>
       <c r="E5" t="n">
-        <v>14.31873997859577</v>
+        <v>14.33958049251806</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.907789827755672</v>
+        <v>2.025131594869416</v>
       </c>
       <c r="C6" t="n">
-        <v>7.142301378581348</v>
+        <v>6.897185866228054</v>
       </c>
       <c r="D6" t="n">
-        <v>6.859559262866099</v>
+        <v>7.021835615645857</v>
       </c>
       <c r="E6" t="n">
-        <v>15.90965046920312</v>
+        <v>15.94415307674333</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.178060941031432</v>
+        <v>2.327448048930554</v>
       </c>
       <c r="C7" t="n">
-        <v>8.255693065055299</v>
+        <v>7.949385950056925</v>
       </c>
       <c r="D7" t="n">
-        <v>7.185740220542044</v>
+        <v>7.441581858850058</v>
       </c>
       <c r="E7" t="n">
-        <v>17.61949422662877</v>
+        <v>17.71841585783754</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.365180563960658</v>
+        <v>1.489782831896673</v>
       </c>
       <c r="C8" t="n">
-        <v>5.800195230807971</v>
+        <v>5.536970520501093</v>
       </c>
       <c r="D8" t="n">
-        <v>5.368593750171657</v>
+        <v>5.811849665090463</v>
       </c>
       <c r="E8" t="n">
-        <v>12.53396954494029</v>
+        <v>12.83860301748823</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.71700107983124</v>
+        <v>1.874042267981988</v>
       </c>
       <c r="C9" t="n">
-        <v>7.172654114578638</v>
+        <v>6.775851300495314</v>
       </c>
       <c r="D9" t="n">
-        <v>5.839663310521936</v>
+        <v>6.411878033346022</v>
       </c>
       <c r="E9" t="n">
-        <v>14.72931850493181</v>
+        <v>15.06177160182332</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.079389047226349</v>
+        <v>2.284389292065788</v>
       </c>
       <c r="C10" t="n">
-        <v>8.720715900525519</v>
+        <v>8.192022442431647</v>
       </c>
       <c r="D10" t="n">
-        <v>6.322705320164265</v>
+        <v>7.020267834838957</v>
       </c>
       <c r="E10" t="n">
-        <v>17.12281026791613</v>
+        <v>17.49667956933639</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.439439801327667</v>
+        <v>2.680694522464026</v>
       </c>
       <c r="C11" t="n">
-        <v>10.36854906601073</v>
+        <v>9.72950665738232</v>
       </c>
       <c r="D11" t="n">
-        <v>6.746327709950255</v>
+        <v>7.693272498376263</v>
       </c>
       <c r="E11" t="n">
-        <v>19.55431657728866</v>
+        <v>20.10347367822261</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.804005271802452</v>
+        <v>3.084830596751694</v>
       </c>
       <c r="C12" t="n">
-        <v>12.15552154635434</v>
+        <v>11.3357636481829</v>
       </c>
       <c r="D12" t="n">
-        <v>7.134385950962036</v>
+        <v>8.317850526603191</v>
       </c>
       <c r="E12" t="n">
-        <v>22.09391276911882</v>
+        <v>22.73844477153779</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.135743805800269</v>
+        <v>3.454985804682922</v>
       </c>
       <c r="C13" t="n">
-        <v>13.96130408884781</v>
+        <v>12.95544721650449</v>
       </c>
       <c r="D13" t="n">
-        <v>7.574699462099344</v>
+        <v>8.949339198105323</v>
       </c>
       <c r="E13" t="n">
-        <v>24.67174735674742</v>
+        <v>25.35977221929273</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.803254548206456</v>
+        <v>1.980774168088365</v>
       </c>
       <c r="C14" t="n">
-        <v>9.812823558349974</v>
+        <v>9.100035455158618</v>
       </c>
       <c r="D14" t="n">
-        <v>5.782788502324987</v>
+        <v>6.829950056105764</v>
       </c>
       <c r="E14" t="n">
-        <v>17.39886660888142</v>
+        <v>17.91075967935275</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.839235601567102</v>
+        <v>2.032335557515407</v>
       </c>
       <c r="C15" t="n">
-        <v>10.67578960785996</v>
+        <v>9.803202430848355</v>
       </c>
       <c r="D15" t="n">
-        <v>5.745707891535585</v>
+        <v>6.949782180886127</v>
       </c>
       <c r="E15" t="n">
-        <v>18.26073310096265</v>
+        <v>18.78532016924989</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.11536196086356</v>
+        <v>2.35096177492871</v>
       </c>
       <c r="C16" t="n">
-        <v>12.6986316650753</v>
+        <v>11.5570750695312</v>
       </c>
       <c r="D16" t="n">
-        <v>6.21207732096099</v>
+        <v>7.515691010045118</v>
       </c>
       <c r="E16" t="n">
-        <v>21.02607094689985</v>
+        <v>21.42372785450502</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.682558485446354</v>
+        <v>1.880115575971939</v>
       </c>
       <c r="C17" t="n">
-        <v>11.73076587336654</v>
+        <v>10.61940783720507</v>
       </c>
       <c r="D17" t="n">
-        <v>5.749301088133128</v>
+        <v>7.034644452441223</v>
       </c>
       <c r="E17" t="n">
-        <v>19.16262544694602</v>
+        <v>19.53416786561823</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.906662033894773</v>
+        <v>2.127643624643687</v>
       </c>
       <c r="C18" t="n">
-        <v>13.73794905469915</v>
+        <v>12.41410154543049</v>
       </c>
       <c r="D18" t="n">
-        <v>6.159701080939422</v>
+        <v>7.502594495670464</v>
       </c>
       <c r="E18" t="n">
-        <v>21.80431216953334</v>
+        <v>22.04433966574464</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.89921056881954</v>
+        <v>2.119151507001953</v>
       </c>
       <c r="C19" t="n">
-        <v>14.70185840315979</v>
+        <v>13.29884275902067</v>
       </c>
       <c r="D19" t="n">
-        <v>6.234029199627948</v>
+        <v>7.650642049470885</v>
       </c>
       <c r="E19" t="n">
-        <v>22.83509817160728</v>
+        <v>23.06863631549351</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.094058035681404</v>
+        <v>2.349449883464169</v>
       </c>
       <c r="C20" t="n">
-        <v>16.78496013446181</v>
+        <v>15.23967943050028</v>
       </c>
       <c r="D20" t="n">
-        <v>6.608909560494594</v>
+        <v>8.155967227800801</v>
       </c>
       <c r="E20" t="n">
-        <v>25.4879277306378</v>
+        <v>25.74509654176525</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.234812809970511</v>
+        <v>1.388957017014303</v>
       </c>
       <c r="C21" t="n">
-        <v>12.25786621577666</v>
+        <v>11.21195148158028</v>
       </c>
       <c r="D21" t="n">
-        <v>5.5110014678813</v>
+        <v>6.868140041800964</v>
       </c>
       <c r="E21" t="n">
-        <v>19.00368049362847</v>
+        <v>19.46904854039554</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_47_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.302068845469541</v>
+        <v>2.606078255237815</v>
       </c>
       <c r="C3" t="n">
-        <v>4.650594725696445</v>
+        <v>7.683704481506422</v>
       </c>
       <c r="D3" t="n">
-        <v>6.117706916824906</v>
+        <v>8.149937101954148</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07037048799089</v>
+        <v>18.43971983869838</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.498152258977249</v>
+        <v>1.116999756966982</v>
       </c>
       <c r="C4" t="n">
-        <v>5.221625386803398</v>
+        <v>4.472542056442431</v>
       </c>
       <c r="D4" t="n">
-        <v>6.31416295383554</v>
+        <v>5.734310233288155</v>
       </c>
       <c r="E4" t="n">
-        <v>13.03394059961619</v>
+        <v>11.32385204669757</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.747805120190746</v>
+        <v>1.259234614298421</v>
       </c>
       <c r="C5" t="n">
-        <v>5.974510172330911</v>
+        <v>5.10340625879135</v>
       </c>
       <c r="D5" t="n">
-        <v>6.617265199996401</v>
+        <v>5.982862429634139</v>
       </c>
       <c r="E5" t="n">
-        <v>14.33958049251806</v>
+        <v>12.34550330272391</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.025131594869416</v>
+        <v>1.416436269362063</v>
       </c>
       <c r="C6" t="n">
-        <v>6.897185866228054</v>
+        <v>5.891500397012503</v>
       </c>
       <c r="D6" t="n">
-        <v>7.021835615645857</v>
+        <v>6.257646799250762</v>
       </c>
       <c r="E6" t="n">
-        <v>15.94415307674333</v>
+        <v>13.56558346562533</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.327448048930554</v>
+        <v>1.580275445698021</v>
       </c>
       <c r="C7" t="n">
-        <v>7.949385950056925</v>
+        <v>6.903786378488078</v>
       </c>
       <c r="D7" t="n">
-        <v>7.441581858850058</v>
+        <v>6.615828887565655</v>
       </c>
       <c r="E7" t="n">
-        <v>17.71841585783754</v>
+        <v>15.09989071175175</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.489782831896673</v>
+        <v>1.743318256062929</v>
       </c>
       <c r="C8" t="n">
-        <v>5.536970520501093</v>
+        <v>8.077871623872969</v>
       </c>
       <c r="D8" t="n">
-        <v>5.811849665090463</v>
+        <v>6.956990514704745</v>
       </c>
       <c r="E8" t="n">
-        <v>12.83860301748823</v>
+        <v>16.77818039464064</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.874042267981988</v>
+        <v>1.911574120980241</v>
       </c>
       <c r="C9" t="n">
-        <v>6.775851300495314</v>
+        <v>9.437366984923587</v>
       </c>
       <c r="D9" t="n">
-        <v>6.411878033346022</v>
+        <v>7.325950990474696</v>
       </c>
       <c r="E9" t="n">
-        <v>15.06177160182332</v>
+        <v>18.67489209637852</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.284389292065788</v>
+        <v>1.170665414975024</v>
       </c>
       <c r="C10" t="n">
-        <v>8.192022442431647</v>
+        <v>7.025474928883556</v>
       </c>
       <c r="D10" t="n">
-        <v>7.020267834838957</v>
+        <v>5.767610682817332</v>
       </c>
       <c r="E10" t="n">
-        <v>17.49667956933639</v>
+        <v>13.96375102667591</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.680694522464026</v>
+        <v>1.121185330680985</v>
       </c>
       <c r="C11" t="n">
-        <v>9.72950665738232</v>
+        <v>7.62926940194943</v>
       </c>
       <c r="D11" t="n">
-        <v>7.693272498376263</v>
+        <v>5.595598667556247</v>
       </c>
       <c r="E11" t="n">
-        <v>20.10347367822261</v>
+        <v>14.34605340018666</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.084830596751694</v>
+        <v>1.229825531632937</v>
       </c>
       <c r="C12" t="n">
-        <v>11.3357636481829</v>
+        <v>9.141622287910515</v>
       </c>
       <c r="D12" t="n">
-        <v>8.317850526603191</v>
+        <v>5.931228755207105</v>
       </c>
       <c r="E12" t="n">
-        <v>22.73844477153779</v>
+        <v>16.30267657475056</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.454985804682922</v>
+        <v>0.9795191369581702</v>
       </c>
       <c r="C13" t="n">
-        <v>12.95544721650449</v>
+        <v>8.789891537910011</v>
       </c>
       <c r="D13" t="n">
-        <v>8.949339198105323</v>
+        <v>5.370395561679072</v>
       </c>
       <c r="E13" t="n">
-        <v>25.35977221929273</v>
+        <v>15.13980623654725</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.980774168088365</v>
+        <v>1.075180633259979</v>
       </c>
       <c r="C14" t="n">
-        <v>9.100035455158618</v>
+        <v>10.34320293809227</v>
       </c>
       <c r="D14" t="n">
-        <v>6.829950056105764</v>
+        <v>5.693685080687546</v>
       </c>
       <c r="E14" t="n">
-        <v>17.91075967935275</v>
+        <v>17.1120686520398</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.032335557515407</v>
+        <v>1.053650906105847</v>
       </c>
       <c r="C15" t="n">
-        <v>9.803202430848355</v>
+        <v>11.19922803133323</v>
       </c>
       <c r="D15" t="n">
-        <v>6.949782180886127</v>
+        <v>5.725356261626549</v>
       </c>
       <c r="E15" t="n">
-        <v>18.78532016924989</v>
+        <v>17.97823519906563</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.35096177492871</v>
+        <v>1.161515526371444</v>
       </c>
       <c r="C16" t="n">
-        <v>11.5570750695312</v>
+        <v>13.04508061242696</v>
       </c>
       <c r="D16" t="n">
-        <v>7.515691010045118</v>
+        <v>6.103898541430034</v>
       </c>
       <c r="E16" t="n">
-        <v>21.42372785450502</v>
+        <v>20.31049468022844</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.880115575971939</v>
+        <v>0.7009187734470104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.61940783720507</v>
+        <v>9.706215575145814</v>
       </c>
       <c r="D17" t="n">
-        <v>7.034644452441223</v>
+        <v>5.05762056058308</v>
       </c>
       <c r="E17" t="n">
-        <v>19.53416786561823</v>
+        <v>15.46475490917591</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.127643624643687</v>
+        <v>0.5664487903963247</v>
       </c>
       <c r="C18" t="n">
-        <v>12.41410154543049</v>
+        <v>8.629179438724806</v>
       </c>
       <c r="D18" t="n">
-        <v>7.502594495670464</v>
+        <v>4.573697482205743</v>
       </c>
       <c r="E18" t="n">
-        <v>22.04433966574464</v>
+        <v>13.76932571132687</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.119151507001953</v>
+        <v>0.6681578525562942</v>
       </c>
       <c r="C19" t="n">
-        <v>13.29884275902067</v>
+        <v>10.63406533042947</v>
       </c>
       <c r="D19" t="n">
-        <v>7.650642049470885</v>
+        <v>5.002593601760047</v>
       </c>
       <c r="E19" t="n">
-        <v>23.06863631549351</v>
+        <v>16.30481678474581</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.349449883464169</v>
+        <v>0.7648207315164351</v>
       </c>
       <c r="C20" t="n">
-        <v>15.23967943050028</v>
+        <v>12.77022070766898</v>
       </c>
       <c r="D20" t="n">
-        <v>8.155967227800801</v>
+        <v>5.462562036153763</v>
       </c>
       <c r="E20" t="n">
-        <v>25.74509654176525</v>
+        <v>18.99760347533918</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.388957017014303</v>
+        <v>0.8487208903213675</v>
       </c>
       <c r="C21" t="n">
-        <v>11.21195148158028</v>
+        <v>14.90347992918096</v>
       </c>
       <c r="D21" t="n">
-        <v>6.868140041800964</v>
+        <v>5.851864270795793</v>
       </c>
       <c r="E21" t="n">
-        <v>19.46904854039554</v>
+        <v>21.60406509029812</v>
       </c>
     </row>
   </sheetData>
